--- a/azure-storage/Azure redundancy.xlsx
+++ b/azure-storage/Azure redundancy.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PersonnelWork\Azure468\Azure468\azure-storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{218C73DF-F835-4C43-9406-37A33466A09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA64FB7-ABD3-44DC-AD9A-5F550908E275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B174891E-1858-4EAD-86E3-C7CC1FE3662D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{B174891E-1858-4EAD-86E3-C7CC1FE3662D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Redundancy Options" sheetId="1" r:id="rId1"/>
+    <sheet name="Blobs Types" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="54">
   <si>
     <t>Redundancy Type</t>
   </si>
@@ -192,6 +193,78 @@
   </si>
   <si>
     <t>Mission-critical apps requiring maximum durability plus secondary read access</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>Block Blob</t>
+  </si>
+  <si>
+    <t>Page Blob</t>
+  </si>
+  <si>
+    <t>Append Blob</t>
+  </si>
+  <si>
+    <t>Primary Use Case</t>
+  </si>
+  <si>
+    <t>General-purpose storage (files, docs, media, backups)</t>
+  </si>
+  <si>
+    <t>Azure VM disks / VHDs and database sparse structures</t>
+  </si>
+  <si>
+    <t>Append-only data (VM logging, audit trails, telemetry)</t>
+  </si>
+  <si>
+    <t>Data Structure</t>
+  </si>
+  <si>
+    <t>Composed of individual data blocks</t>
+  </si>
+  <si>
+    <t>Collection of 512-byte pages</t>
+  </si>
+  <si>
+    <t>Composed of blocks optimized for sequential appends</t>
+  </si>
+  <si>
+    <t>Write Operations</t>
+  </si>
+  <si>
+    <t>Random reads/writes, overwriting, parallel chunk uploads</t>
+  </si>
+  <si>
+    <t>Frequent random read/write in-place updates</t>
+  </si>
+  <si>
+    <t>Append-only to the end; existing blocks cannot be modified or deleted</t>
+  </si>
+  <si>
+    <t>Maximum Size</t>
+  </si>
+  <si>
+    <t>Up to ~190.7 TiB</t>
+  </si>
+  <si>
+    <t>Up to 8 TiB</t>
+  </si>
+  <si>
+    <t>Up to ~4.75 TiB (via 100 MiB blocks) or ~195 GiB (legacy 4 MiB blocks)</t>
+  </si>
+  <si>
+    <t>Default Choice</t>
+  </si>
+  <si>
+    <t>Yes (default when uploading a general file)</t>
+  </si>
+  <si>
+    <t>No (managed by Azure for IaaS disks)</t>
+  </si>
+  <si>
+    <t>No (must be explicitly created via API/SDK)</t>
   </si>
 </sst>
 </file>
@@ -255,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -266,9 +339,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -587,8 +668,7 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="31.54296875" defaultRowHeight="55" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="6" width="25.81640625" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="31.54296875" style="4"/>
+    <col min="1" max="6" width="25.81640625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="55" customHeight="1" x14ac:dyDescent="0.35">
@@ -734,4 +814,101 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA3C6E7-8702-4290-B70E-25CE0171FC41}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="45" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="54" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="54" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="36" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>